--- a/experiment/Omni_bestx4/Test/results-Urban100/Urban100.xlsx
+++ b/experiment/Omni_bestx4/Test/results-Urban100/Urban100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.38</v>
+        <v>27.6</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7609</v>
+        <v>0.7683</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.6</v>
+        <v>26.82</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8219</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.88</v>
+        <v>23.95</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6858</v>
+        <v>0.6914</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.92</v>
+        <v>23.34</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8268</v>
+        <v>0.8369</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.99</v>
+        <v>28.19</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9503</v>
+        <v>0.9529</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.43</v>
+        <v>22.61</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6248</v>
+        <v>0.6335</v>
       </c>
     </row>
     <row r="8">
@@ -533,7 +533,7 @@
         <v>29.61</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8625</v>
+        <v>0.8635</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.51</v>
+        <v>21.57</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6585</v>
+        <v>0.671</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33.88</v>
+        <v>33.91</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9267</v>
+        <v>0.929</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>27.27</v>
+        <v>27.59</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8868</v>
+        <v>0.8933</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17.92</v>
+        <v>17.96</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7843</v>
+        <v>0.7923</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23.88</v>
+        <v>23.85</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7323</v>
+        <v>0.7361</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29.56</v>
+        <v>29.67</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8378</v>
+        <v>0.842</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22.38</v>
+        <v>22.43</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6928</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26.14</v>
+        <v>26.31</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7357</v>
+        <v>0.7409</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>30.13</v>
+        <v>30.7</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9127999999999999</v>
+        <v>0.918</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25.77</v>
+        <v>25.89</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8274</v>
+        <v>0.8334</v>
       </c>
     </row>
     <row r="19">
@@ -676,7 +676,7 @@
         <v>26.39</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7154</v>
+        <v>0.7166</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>22.06</v>
+        <v>22.12</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8115</v>
+        <v>0.8168</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.13</v>
+        <v>22.17</v>
       </c>
       <c r="C21" t="n">
-        <v>0.718</v>
+        <v>0.723</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29.71</v>
+        <v>29.67</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7851</v>
+        <v>0.7862</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26.09</v>
+        <v>26.12</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7601</v>
+        <v>0.7627</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30.46</v>
+        <v>30.61</v>
       </c>
       <c r="C24" t="n">
-        <v>0.9136</v>
+        <v>0.9188</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>20.14</v>
+        <v>20.32</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6499</v>
+        <v>0.6673</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>31.99</v>
+        <v>32.19</v>
       </c>
       <c r="C26" t="n">
-        <v>0.9002</v>
+        <v>0.9022</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27.85</v>
+        <v>28.04</v>
       </c>
       <c r="C27" t="n">
-        <v>0.698</v>
+        <v>0.7082000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28.28</v>
+        <v>28.4</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7945</v>
+        <v>0.7998</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.49</v>
+        <v>31.51</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8774999999999999</v>
+        <v>0.8781</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26.72</v>
+        <v>27.32</v>
       </c>
       <c r="C30" t="n">
-        <v>0.857</v>
+        <v>0.8722</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>24.72</v>
+        <v>24.92</v>
       </c>
       <c r="C31" t="n">
-        <v>0.8147</v>
+        <v>0.8225</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24.26</v>
+        <v>24.32</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7914</v>
+        <v>0.796</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29.15</v>
+        <v>29.18</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8532999999999999</v>
+        <v>0.856</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>27.04</v>
+        <v>27.45</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7958</v>
+        <v>0.8126</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>23.07</v>
+        <v>23.13</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5862000000000001</v>
+        <v>0.5895</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>28.9</v>
+        <v>29.37</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8706</v>
+        <v>0.882</v>
       </c>
     </row>
     <row r="37">
@@ -910,7 +910,7 @@
         <v>28.8</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8852</v>
+        <v>0.8868</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26.53</v>
+        <v>26.55</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8013</v>
+        <v>0.8041</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>27.15</v>
+        <v>27.24</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6874</v>
+        <v>0.6955</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>22.96</v>
+        <v>23.08</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7388</v>
+        <v>0.7511</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>27.53</v>
+        <v>28.4</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9419</v>
+        <v>0.9506</v>
       </c>
     </row>
     <row r="42">
@@ -975,7 +975,7 @@
         <v>26.45</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8822</v>
+        <v>0.8853</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29.07</v>
+        <v>29.06</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8881</v>
+        <v>0.8893</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>31.49</v>
+        <v>32.51</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9296</v>
+        <v>0.9357</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>32.18</v>
+        <v>32.05</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8707</v>
+        <v>0.8712</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.78</v>
+        <v>24.63</v>
       </c>
       <c r="C46" t="n">
-        <v>0.73</v>
+        <v>0.7241</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23.59</v>
+        <v>23.72</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7542</v>
+        <v>0.7624</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.03</v>
+        <v>22.07</v>
       </c>
       <c r="C48" t="n">
-        <v>0.772</v>
+        <v>0.7827</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20.56</v>
+        <v>20.55</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8196</v>
+        <v>0.8236</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>23.52</v>
+        <v>23.64</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7504999999999999</v>
+        <v>0.7564</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25.24</v>
+        <v>25.31</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7675999999999999</v>
+        <v>0.7741</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>27.44</v>
+        <v>27.53</v>
       </c>
       <c r="C52" t="n">
-        <v>0.8488</v>
+        <v>0.8527</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28.75</v>
+        <v>29.19</v>
       </c>
       <c r="C53" t="n">
-        <v>0.9029</v>
+        <v>0.9114</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>22.38</v>
+        <v>22.48</v>
       </c>
       <c r="C54" t="n">
-        <v>0.7274</v>
+        <v>0.733</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>21.24</v>
+        <v>21.28</v>
       </c>
       <c r="C55" t="n">
-        <v>0.6499</v>
+        <v>0.6577</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>32.65</v>
+        <v>33.5</v>
       </c>
       <c r="C56" t="n">
-        <v>0.9442</v>
+        <v>0.9500999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.05</v>
+        <v>25.18</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7823</v>
+        <v>0.7911</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>30.95</v>
+        <v>31.23</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8954</v>
+        <v>0.901</v>
       </c>
     </row>
     <row r="59">
@@ -1196,7 +1196,7 @@
         <v>25.97</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8614000000000001</v>
+        <v>0.8647</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>21.78</v>
+        <v>22.03</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7511</v>
+        <v>0.763</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>22.55</v>
+        <v>22.61</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5647</v>
+        <v>0.5715</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24.75</v>
+        <v>24.79</v>
       </c>
       <c r="C62" t="n">
-        <v>0.7547</v>
+        <v>0.7617</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>21.82</v>
+        <v>22.14</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8078</v>
+        <v>0.8224</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>22.37</v>
+        <v>22.46</v>
       </c>
       <c r="C64" t="n">
-        <v>0.6179</v>
+        <v>0.6234</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>26.63</v>
+        <v>26.67</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7866</v>
+        <v>0.7889</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.42</v>
+        <v>25.5</v>
       </c>
       <c r="C66" t="n">
-        <v>0.7212</v>
+        <v>0.7289</v>
       </c>
     </row>
     <row r="67">
@@ -1300,7 +1300,7 @@
         <v>22.28</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6446</v>
+        <v>0.6473</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>20.17</v>
+        <v>20.47</v>
       </c>
       <c r="C68" t="n">
-        <v>0.8758</v>
+        <v>0.8874</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>30.46</v>
+        <v>30.41</v>
       </c>
       <c r="C69" t="n">
-        <v>0.8839</v>
+        <v>0.8879</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>24.75</v>
+        <v>24.9</v>
       </c>
       <c r="C70" t="n">
-        <v>0.7502</v>
+        <v>0.7589</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>22.14</v>
+        <v>22.16</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5952</v>
+        <v>0.5991</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>27.95</v>
+        <v>28.07</v>
       </c>
       <c r="C72" t="n">
-        <v>0.6627999999999999</v>
+        <v>0.6692</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>20.23</v>
+        <v>20.36</v>
       </c>
       <c r="C73" t="n">
-        <v>0.8161</v>
+        <v>0.8255</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>19.89</v>
+        <v>20.53</v>
       </c>
       <c r="C74" t="n">
-        <v>0.5618</v>
+        <v>0.5837</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>23.68</v>
+        <v>23.86</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6981000000000001</v>
+        <v>0.717</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>31.66</v>
+        <v>31.85</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8849</v>
+        <v>0.8883</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>22.99</v>
+        <v>22.74</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7319</v>
+        <v>0.7317</v>
       </c>
     </row>
     <row r="78">
@@ -1443,7 +1443,7 @@
         <v>22.73</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6744</v>
+        <v>0.6766</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>27.29</v>
+        <v>27.24</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7698</v>
+        <v>0.7725</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>25.41</v>
+        <v>25.51</v>
       </c>
       <c r="C80" t="n">
-        <v>0.6952</v>
+        <v>0.6995</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35.51</v>
+        <v>35.71</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9517</v>
+        <v>0.9542</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>36.36</v>
+        <v>37.56</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9656</v>
+        <v>0.9724</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>32.89</v>
+        <v>32.9</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9415</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.23</v>
+        <v>22.28</v>
       </c>
       <c r="C84" t="n">
-        <v>0.6934</v>
+        <v>0.7020999999999999</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>28.61</v>
+        <v>28.71</v>
       </c>
       <c r="C85" t="n">
-        <v>0.8094</v>
+        <v>0.8127</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>28.4</v>
+        <v>28.36</v>
       </c>
       <c r="C86" t="n">
-        <v>0.9033</v>
+        <v>0.9038</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>30.45</v>
+        <v>30.39</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8851</v>
+        <v>0.8854</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.67</v>
+        <v>28.08</v>
       </c>
       <c r="C88" t="n">
-        <v>0.8804</v>
+        <v>0.8898</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>19.9</v>
+        <v>19.88</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5703</v>
+        <v>0.5765</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>26.74</v>
+        <v>26.78</v>
       </c>
       <c r="C90" t="n">
-        <v>0.7153</v>
+        <v>0.7191</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>38.29</v>
+        <v>38.3</v>
       </c>
       <c r="C91" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.9766</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>24.07</v>
+        <v>24.04</v>
       </c>
       <c r="C92" t="n">
-        <v>0.6824</v>
+        <v>0.6852</v>
       </c>
     </row>
     <row r="93">
@@ -1638,7 +1638,7 @@
         <v>18.95</v>
       </c>
       <c r="C93" t="n">
-        <v>0.65</v>
+        <v>0.6602</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>29.38</v>
+        <v>28.73</v>
       </c>
       <c r="C94" t="n">
-        <v>0.9293</v>
+        <v>0.9244</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>27.11</v>
+        <v>27.27</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7815</v>
+        <v>0.7874</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>20.1</v>
+        <v>20.13</v>
       </c>
       <c r="C96" t="n">
-        <v>0.4396</v>
+        <v>0.4506</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>25.14</v>
+        <v>25.61</v>
       </c>
       <c r="C97" t="n">
-        <v>0.8643</v>
+        <v>0.8754</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>24.86</v>
+        <v>24.96</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7602</v>
+        <v>0.7671</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>20.72</v>
+        <v>20.78</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5308</v>
+        <v>0.5397999999999999</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>25.73</v>
+        <v>26.12</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7901</v>
+        <v>0.8064</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>26.16</v>
+        <v>26.29</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7436</v>
+        <v>0.7488</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>26.02</v>
+        <v>26.17</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7825</v>
+        <v>0.7887</v>
       </c>
     </row>
   </sheetData>
